--- a/output/roomself_excel/3501.xlsx
+++ b/output/roomself_excel/3501.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53326</v>
+        <v>14875</v>
       </c>
       <c r="D2" t="n">
-        <v>1314</v>
+        <v>976</v>
       </c>
       <c r="E2" t="n">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>275868</v>
+        <v>12250</v>
       </c>
       <c r="D3" t="n">
-        <v>2974</v>
+        <v>892</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100492</v>
+        <v>12875</v>
       </c>
       <c r="D4" t="n">
-        <v>2070</v>
+        <v>912</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>345320</v>
+        <v>11750</v>
       </c>
       <c r="D5" t="n">
-        <v>3332</v>
+        <v>876</v>
       </c>
       <c r="E5" t="n">
-        <v>388</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14875</v>
+        <v>16124</v>
       </c>
       <c r="D6" t="n">
-        <v>976</v>
+        <v>1020</v>
       </c>
       <c r="E6" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>485611</v>
+        <v>13622</v>
       </c>
       <c r="D7" t="n">
-        <v>11608</v>
+        <v>948</v>
       </c>
       <c r="E7" t="n">
-        <v>2257</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>719</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12250</v>
+        <v>16137</v>
       </c>
       <c r="D8" t="n">
-        <v>892</v>
+        <v>1048</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12875</v>
+        <v>16300</v>
       </c>
       <c r="D9" t="n">
-        <v>912</v>
+        <v>1052</v>
       </c>
       <c r="E9" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11750</v>
+        <v>15974</v>
       </c>
       <c r="D10" t="n">
-        <v>876</v>
+        <v>1044</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F10" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>271152</v>
+        <v>15974</v>
       </c>
       <c r="D11" t="n">
-        <v>4364</v>
+        <v>1044</v>
       </c>
       <c r="E11" t="n">
-        <v>632</v>
+        <v>98</v>
       </c>
       <c r="F11" t="n">
-        <v>470</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16124</v>
+        <v>53326</v>
       </c>
       <c r="D12" t="n">
-        <v>1020</v>
+        <v>1314</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -712,16 +712,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>153267</v>
+        <v>275868</v>
       </c>
       <c r="D13" t="n">
-        <v>3968</v>
+        <v>2974</v>
       </c>
       <c r="E13" t="n">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>258315</v>
+        <v>100492</v>
       </c>
       <c r="D14" t="n">
-        <v>4248</v>
+        <v>2070</v>
       </c>
       <c r="E14" t="n">
-        <v>411</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -756,13 +756,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>281232</v>
+        <v>345320</v>
       </c>
       <c r="D15" t="n">
-        <v>4332</v>
+        <v>3332</v>
       </c>
       <c r="E15" t="n">
-        <v>432</v>
+        <v>388</v>
       </c>
       <c r="F15" t="n">
         <v>30</v>
@@ -778,16 +778,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24939</v>
+        <v>485611</v>
       </c>
       <c r="D16" t="n">
-        <v>1264</v>
+        <v>11608</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>349</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13622</v>
+        <v>271152</v>
       </c>
       <c r="D17" t="n">
-        <v>948</v>
+        <v>4364</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>470</v>
       </c>
     </row>
     <row r="18">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>88050</v>
+        <v>153267</v>
       </c>
       <c r="D18" t="n">
-        <v>2972</v>
+        <v>3968</v>
       </c>
       <c r="E18" t="n">
-        <v>513</v>
+        <v>275</v>
       </c>
       <c r="F18" t="n">
-        <v>290</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>150885</v>
+        <v>258315</v>
       </c>
       <c r="D19" t="n">
-        <v>3176</v>
+        <v>4248</v>
       </c>
       <c r="E19" t="n">
-        <v>332</v>
+        <v>411</v>
       </c>
       <c r="F19" t="n">
-        <v>247</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>67462</v>
+        <v>281232</v>
       </c>
       <c r="D20" t="n">
-        <v>2112</v>
+        <v>4332</v>
       </c>
       <c r="E20" t="n">
-        <v>337</v>
+        <v>432</v>
       </c>
       <c r="F20" t="n">
-        <v>251</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>248832</v>
+        <v>24939</v>
       </c>
       <c r="D21" t="n">
-        <v>4032</v>
+        <v>1264</v>
       </c>
       <c r="E21" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>177808</v>
+        <v>88050</v>
       </c>
       <c r="D22" t="n">
-        <v>3544</v>
+        <v>2972</v>
       </c>
       <c r="E22" t="n">
-        <v>414</v>
+        <v>513</v>
       </c>
       <c r="F22" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>189798</v>
+        <v>150885</v>
       </c>
       <c r="D23" t="n">
-        <v>3488</v>
+        <v>3176</v>
       </c>
       <c r="E23" t="n">
-        <v>440</v>
+        <v>332</v>
       </c>
       <c r="F23" t="n">
-        <v>77</v>
+        <v>247</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>176603</v>
+        <v>67462</v>
       </c>
       <c r="D24" t="n">
-        <v>3368</v>
+        <v>2112</v>
       </c>
       <c r="E24" t="n">
-        <v>462</v>
+        <v>337</v>
       </c>
       <c r="F24" t="n">
-        <v>440</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25">
@@ -972,17 +972,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>16137</v>
+        <v>248832</v>
       </c>
       <c r="D25" t="n">
-        <v>1048</v>
+        <v>4032</v>
       </c>
       <c r="E25" t="n">
-        <v>99</v>
+        <v>576</v>
       </c>
       <c r="F25" t="n">
         <v>30</v>
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>338991</v>
+        <v>177808</v>
       </c>
       <c r="D26" t="n">
-        <v>8716</v>
+        <v>3544</v>
       </c>
       <c r="E26" t="n">
-        <v>221</v>
+        <v>414</v>
       </c>
       <c r="F26" t="n">
-        <v>202</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16300</v>
+        <v>189798</v>
       </c>
       <c r="D27" t="n">
-        <v>1052</v>
+        <v>3488</v>
       </c>
       <c r="E27" t="n">
-        <v>100</v>
+        <v>440</v>
       </c>
       <c r="F27" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28">
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>209045</v>
+        <v>176603</v>
       </c>
       <c r="D28" t="n">
-        <v>6040</v>
+        <v>3368</v>
       </c>
       <c r="E28" t="n">
-        <v>880</v>
+        <v>462</v>
       </c>
       <c r="F28" t="n">
-        <v>287</v>
+        <v>440</v>
       </c>
     </row>
     <row r="29">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15974</v>
+        <v>338991</v>
       </c>
       <c r="D29" t="n">
-        <v>1044</v>
+        <v>8716</v>
       </c>
       <c r="E29" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15974</v>
+        <v>209045</v>
       </c>
       <c r="D30" t="n">
-        <v>1044</v>
+        <v>6040</v>
       </c>
       <c r="E30" t="n">
-        <v>98</v>
+        <v>880</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31">
@@ -1114,7 +1114,7 @@
         <v>6240</v>
       </c>
       <c r="E31" t="n">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="F31" t="n">
         <v>655</v>
@@ -1136,10 +1136,10 @@
         <v>4844</v>
       </c>
       <c r="E32" t="n">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="F32" t="n">
-        <v>196</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1158,10 +1158,10 @@
         <v>4364</v>
       </c>
       <c r="E33" t="n">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="F33" t="n">
-        <v>193</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34">

--- a/output/roomself_excel/3501.xlsx
+++ b/output/roomself_excel/3501.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>976</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>119</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>75</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +525,20 @@
       <c r="D3" t="n">
         <v>892</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>98</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>75</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +555,20 @@
       <c r="D4" t="n">
         <v>912</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>103</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>75</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +585,20 @@
       <c r="D5" t="n">
         <v>876</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>94</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>75</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +615,12 @@
       <c r="D6" t="n">
         <v>1020</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +637,12 @@
       <c r="D7" t="n">
         <v>948</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +659,20 @@
       <c r="D8" t="n">
         <v>1048</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>99</v>
       </c>
-      <c r="F8" t="n">
-        <v>30</v>
-      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +689,20 @@
       <c r="D9" t="n">
         <v>1052</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>100</v>
       </c>
-      <c r="F9" t="n">
-        <v>30</v>
-      </c>
+      <c r="G9" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +719,20 @@
       <c r="D10" t="n">
         <v>1044</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>98</v>
       </c>
-      <c r="F10" t="n">
-        <v>30</v>
-      </c>
+      <c r="G10" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +749,20 @@
       <c r="D11" t="n">
         <v>1044</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>98</v>
       </c>
-      <c r="F11" t="n">
-        <v>30</v>
-      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +779,20 @@
       <c r="D12" t="n">
         <v>1314</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>182</v>
       </c>
-      <c r="F12" t="n">
-        <v>30</v>
-      </c>
+      <c r="G12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +809,12 @@
       <c r="D13" t="n">
         <v>2974</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +831,12 @@
       <c r="D14" t="n">
         <v>2070</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +853,20 @@
       <c r="D15" t="n">
         <v>3332</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>388</v>
       </c>
-      <c r="F15" t="n">
-        <v>30</v>
-      </c>
+      <c r="G15" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +883,20 @@
       <c r="D16" t="n">
         <v>11608</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>349</v>
       </c>
-      <c r="F16" t="n">
-        <v>30</v>
-      </c>
+      <c r="G16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,11 +913,27 @@
       <c r="D17" t="n">
         <v>4364</v>
       </c>
-      <c r="E17" t="n">
-        <v>632</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>470</v>
+        <v>602</v>
+      </c>
+      <c r="G17" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>440</v>
+      </c>
+      <c r="J17" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -827,12 +951,20 @@
       <c r="D18" t="n">
         <v>3968</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>275</v>
       </c>
-      <c r="F18" t="n">
-        <v>30</v>
-      </c>
+      <c r="G18" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +981,20 @@
       <c r="D19" t="n">
         <v>4248</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>411</v>
       </c>
-      <c r="F19" t="n">
-        <v>30</v>
-      </c>
+      <c r="G19" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1011,20 @@
       <c r="D20" t="n">
         <v>4332</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>432</v>
       </c>
-      <c r="F20" t="n">
-        <v>30</v>
-      </c>
+      <c r="G20" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1041,12 @@
       <c r="D21" t="n">
         <v>1264</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,11 +1063,27 @@
       <c r="D22" t="n">
         <v>2972</v>
       </c>
-      <c r="E22" t="n">
-        <v>513</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>290</v>
+        <v>483</v>
+      </c>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>260</v>
+      </c>
+      <c r="J22" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="23">
@@ -937,12 +1101,20 @@
       <c r="D23" t="n">
         <v>3176</v>
       </c>
-      <c r="E23" t="n">
-        <v>332</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>247</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -959,11 +1131,27 @@
       <c r="D24" t="n">
         <v>2112</v>
       </c>
-      <c r="E24" t="n">
-        <v>337</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>251</v>
+        <v>296</v>
+      </c>
+      <c r="G24" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>221</v>
+      </c>
+      <c r="J24" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -981,12 +1169,20 @@
       <c r="D25" t="n">
         <v>4032</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>576</v>
       </c>
-      <c r="F25" t="n">
-        <v>30</v>
-      </c>
+      <c r="G25" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1199,20 @@
       <c r="D26" t="n">
         <v>3544</v>
       </c>
-      <c r="E26" t="n">
-        <v>414</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F26" t="n">
-        <v>70</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="G26" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1229,20 @@
       <c r="D27" t="n">
         <v>3488</v>
       </c>
-      <c r="E27" t="n">
-        <v>440</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>77</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,11 +1259,27 @@
       <c r="D28" t="n">
         <v>3368</v>
       </c>
-      <c r="E28" t="n">
-        <v>462</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>440</v>
+        <v>399</v>
+      </c>
+      <c r="G28" t="n">
+        <v>30</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>432</v>
+      </c>
+      <c r="J28" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="29">
@@ -1069,12 +1297,12 @@
       <c r="D29" t="n">
         <v>8716</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,11 +1319,27 @@
       <c r="D30" t="n">
         <v>6040</v>
       </c>
-      <c r="E30" t="n">
-        <v>880</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>287</v>
+        <v>830</v>
+      </c>
+      <c r="G30" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>257</v>
+      </c>
+      <c r="J30" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -1113,11 +1357,27 @@
       <c r="D31" t="n">
         <v>6240</v>
       </c>
-      <c r="E31" t="n">
-        <v>771</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>655</v>
+        <v>625</v>
+      </c>
+      <c r="G31" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>741</v>
+      </c>
+      <c r="J31" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -1135,12 +1395,20 @@
       <c r="D32" t="n">
         <v>4844</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>389</v>
       </c>
-      <c r="F32" t="n">
-        <v>30</v>
-      </c>
+      <c r="G32" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1157,12 +1425,20 @@
       <c r="D33" t="n">
         <v>4364</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>269</v>
       </c>
-      <c r="F33" t="n">
-        <v>30</v>
-      </c>
+      <c r="G33" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1179,12 +1455,20 @@
       <c r="D34" t="n">
         <v>1264</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>153</v>
       </c>
-      <c r="F34" t="n">
-        <v>30</v>
-      </c>
+      <c r="G34" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1201,12 +1485,20 @@
       <c r="D35" t="n">
         <v>1256</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>156</v>
       </c>
-      <c r="F35" t="n">
-        <v>30</v>
-      </c>
+      <c r="G35" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1223,12 +1515,20 @@
       <c r="D36" t="n">
         <v>1244</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>156</v>
       </c>
-      <c r="F36" t="n">
-        <v>30</v>
-      </c>
+      <c r="G36" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/3501.xlsx
+++ b/output/roomself_excel/3501.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,26 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -509,6 +529,10 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -539,6 +563,10 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -569,6 +597,10 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -599,6 +631,10 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -621,6 +657,10 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -643,6 +683,10 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -673,6 +717,10 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -703,6 +751,10 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -733,6 +785,10 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -763,6 +819,10 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -793,6 +853,10 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -815,6 +879,10 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -837,6 +905,10 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -867,6 +939,10 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -897,6 +973,22 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>159</v>
+      </c>
+      <c r="N16" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -935,6 +1027,22 @@
       <c r="J17" t="n">
         <v>30</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>388</v>
+      </c>
+      <c r="N17" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -965,6 +1073,22 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>260</v>
+      </c>
+      <c r="N18" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -995,6 +1119,22 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>260</v>
+      </c>
+      <c r="N19" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1025,6 +1165,22 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>414</v>
+      </c>
+      <c r="N20" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1047,6 +1203,10 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1085,6 +1245,22 @@
       <c r="J22" t="n">
         <v>30</v>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>244</v>
+      </c>
+      <c r="N22" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1115,6 +1291,22 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>280</v>
+      </c>
+      <c r="N23" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1153,6 +1345,10 @@
       <c r="J24" t="n">
         <v>30</v>
       </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1183,6 +1379,22 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>540</v>
+      </c>
+      <c r="N25" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1213,6 +1425,22 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>235</v>
+      </c>
+      <c r="N26" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1243,6 +1471,22 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>395</v>
+      </c>
+      <c r="N27" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1279,6 +1523,22 @@
         <v>432</v>
       </c>
       <c r="J28" t="n">
+        <v>30</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>373</v>
+      </c>
+      <c r="N28" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1303,6 +1563,10 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1341,6 +1605,10 @@
       <c r="J30" t="n">
         <v>30</v>
       </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1377,6 +1645,22 @@
         <v>741</v>
       </c>
       <c r="J31" t="n">
+        <v>30</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>718</v>
+      </c>
+      <c r="N31" t="n">
         <v>30</v>
       </c>
     </row>
@@ -1409,6 +1693,22 @@
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>368</v>
+      </c>
+      <c r="N32" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1439,6 +1739,22 @@
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>255</v>
+      </c>
+      <c r="N33" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1469,6 +1785,22 @@
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>146</v>
+      </c>
+      <c r="N34" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1499,6 +1831,22 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>143</v>
+      </c>
+      <c r="N35" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1529,6 +1877,22 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>144</v>
+      </c>
+      <c r="N36" t="n">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
